--- a/backend/queue/class8_cbse_queue.xlsx
+++ b/backend/queue/class8_cbse_queue.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="queue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="queue" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'queue'!$A$1:$S$1</definedName>
@@ -600,14 +600,32 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>354</v>
+      </c>
+      <c r="M2" t="n">
+        <v>16</v>
+      </c>
+      <c r="N2" t="n">
+        <v>31527</v>
+      </c>
+      <c r="O2" t="n">
+        <v>34</v>
+      </c>
+      <c r="P2" t="n">
+        <v>504.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2026-09-19T11:38:21</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -654,19 +672,33 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
-      <c r="O3" s="2" t="n"/>
-      <c r="P3" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>439</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>27458</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>701.3</v>
+      </c>
       <c r="Q3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T01:54:52</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -713,14 +745,32 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>440</v>
+      </c>
+      <c r="M4" t="n">
+        <v>8</v>
+      </c>
+      <c r="N4" t="n">
+        <v>14137</v>
+      </c>
+      <c r="O4" t="n">
+        <v>12</v>
+      </c>
+      <c r="P4" t="n">
+        <v>440.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2026-09-20T02:02:12</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -767,19 +817,33 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n"/>
-      <c r="M5" s="2" t="n"/>
-      <c r="N5" s="2" t="n"/>
-      <c r="O5" s="2" t="n"/>
-      <c r="P5" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>441</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>26451</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>599.4</v>
+      </c>
       <c r="Q5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T02:12:12</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -826,14 +890,32 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>442</v>
+      </c>
+      <c r="M6" t="n">
+        <v>13</v>
+      </c>
+      <c r="N6" t="n">
+        <v>24150</v>
+      </c>
+      <c r="O6" t="n">
+        <v>15</v>
+      </c>
+      <c r="P6" t="n">
+        <v>369.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2026-09-20T02:18:22</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -880,19 +962,33 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="n"/>
-      <c r="M7" s="2" t="n"/>
-      <c r="N7" s="2" t="n"/>
-      <c r="O7" s="2" t="n"/>
-      <c r="P7" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>443</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>23366</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>388.6</v>
+      </c>
       <c r="Q7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" s="2" t="inlineStr"/>
-      <c r="S7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T02:24:52</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -939,14 +1035,32 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>444</v>
+      </c>
+      <c r="M8" t="n">
+        <v>14</v>
+      </c>
+      <c r="N8" t="n">
+        <v>28082</v>
+      </c>
+      <c r="O8" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" t="n">
+        <v>595.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2026-09-20T02:34:48</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -993,19 +1107,33 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n"/>
-      <c r="M9" s="2" t="n"/>
-      <c r="N9" s="2" t="n"/>
-      <c r="O9" s="2" t="n"/>
-      <c r="P9" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>445</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>36999</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>739.4</v>
+      </c>
       <c r="Q9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="2" t="inlineStr"/>
-      <c r="S9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T02:47:09</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1052,14 +1180,32 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>446</v>
+      </c>
+      <c r="M10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N10" t="n">
+        <v>19691</v>
+      </c>
+      <c r="O10" t="n">
+        <v>21</v>
+      </c>
+      <c r="P10" t="n">
+        <v>327.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2026-09-20T02:52:37</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1106,19 +1252,33 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2" t="n"/>
-      <c r="N11" s="2" t="n"/>
-      <c r="O11" s="2" t="n"/>
-      <c r="P11" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>447</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>26693</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>472.8</v>
+      </c>
       <c r="Q11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" s="2" t="inlineStr"/>
-      <c r="S11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T03:00:31</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1165,14 +1325,32 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>448</v>
+      </c>
+      <c r="M12" t="n">
+        <v>12</v>
+      </c>
+      <c r="N12" t="n">
+        <v>24303</v>
+      </c>
+      <c r="O12" t="n">
+        <v>18</v>
+      </c>
+      <c r="P12" t="n">
+        <v>363.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2026-09-20T03:06:35</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1219,19 +1397,33 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n"/>
-      <c r="M13" s="2" t="n"/>
-      <c r="N13" s="2" t="n"/>
-      <c r="O13" s="2" t="n"/>
-      <c r="P13" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>449</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>26949</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>413.8</v>
+      </c>
       <c r="Q13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T03:13:29</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1278,14 +1470,32 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>450</v>
+      </c>
+      <c r="M14" t="n">
+        <v>16</v>
+      </c>
+      <c r="N14" t="n">
+        <v>31753</v>
+      </c>
+      <c r="O14" t="n">
+        <v>26</v>
+      </c>
+      <c r="P14" t="n">
+        <v>449.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2026-09-20T03:21:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1332,14 +1542,32 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>451</v>
+      </c>
+      <c r="M15" t="n">
+        <v>13</v>
+      </c>
+      <c r="N15" t="n">
+        <v>22063</v>
+      </c>
+      <c r="O15" t="n">
+        <v>14</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1195.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2026-09-20T03:40:56</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1386,19 +1614,33 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n"/>
-      <c r="M16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
-      <c r="O16" s="2" t="n"/>
-      <c r="P16" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>452</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>8518</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>179.3</v>
+      </c>
       <c r="Q16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T03:43:56</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1445,14 +1687,32 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>453</v>
+      </c>
+      <c r="M17" t="n">
+        <v>16</v>
+      </c>
+      <c r="N17" t="n">
+        <v>36912</v>
+      </c>
+      <c r="O17" t="n">
+        <v>76</v>
+      </c>
+      <c r="P17" t="n">
+        <v>378.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2026-09-20T03:50:16</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1499,19 +1759,33 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n"/>
-      <c r="M18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-      <c r="O18" s="2" t="n"/>
-      <c r="P18" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>454</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>23662</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>1315.4</v>
+      </c>
       <c r="Q18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" s="2" t="inlineStr"/>
-      <c r="S18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:12:12</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1558,14 +1832,32 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>455</v>
+      </c>
+      <c r="M19" t="n">
+        <v>20</v>
+      </c>
+      <c r="N19" t="n">
+        <v>41584</v>
+      </c>
+      <c r="O19" t="n">
+        <v>40</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1914.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:44:07</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1612,19 +1904,33 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2" t="n"/>
-      <c r="N20" s="2" t="n"/>
-      <c r="O20" s="2" t="n"/>
-      <c r="P20" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>456</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>14133</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>490.4</v>
+      </c>
       <c r="Q20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" s="2" t="inlineStr"/>
-      <c r="S20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:52:18</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1671,14 +1977,32 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>457</v>
+      </c>
+      <c r="M21" t="n">
+        <v>13</v>
+      </c>
+      <c r="N21" t="n">
+        <v>25826</v>
+      </c>
+      <c r="O21" t="n">
+        <v>20</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1037.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>2026-09-20T05:09:37</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1725,19 +2049,33 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n"/>
-      <c r="M22" s="2" t="n"/>
-      <c r="N22" s="2" t="n"/>
-      <c r="O22" s="2" t="n"/>
-      <c r="P22" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>458</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>25760</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>892.4</v>
+      </c>
       <c r="Q22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" s="2" t="inlineStr"/>
-      <c r="S22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T05:24:32</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1784,14 +2122,32 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>459</v>
+      </c>
+      <c r="M23" t="n">
+        <v>18</v>
+      </c>
+      <c r="N23" t="n">
+        <v>43595</v>
+      </c>
+      <c r="O23" t="n">
+        <v>75</v>
+      </c>
+      <c r="P23" t="n">
+        <v>656.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>2026-09-20T05:35:29</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1838,19 +2194,33 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n"/>
-      <c r="M24" s="2" t="n"/>
-      <c r="N24" s="2" t="n"/>
-      <c r="O24" s="2" t="n"/>
-      <c r="P24" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>460</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>16707</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>337.2</v>
+      </c>
       <c r="Q24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" s="2" t="inlineStr"/>
-      <c r="S24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T05:41:07</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1897,14 +2267,32 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>461</v>
+      </c>
+      <c r="M25" t="n">
+        <v>16</v>
+      </c>
+      <c r="N25" t="n">
+        <v>34762</v>
+      </c>
+      <c r="O25" t="n">
+        <v>57</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1686.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>2026-09-20T06:09:15</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1951,19 +2339,33 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n"/>
-      <c r="M26" s="2" t="n"/>
-      <c r="N26" s="2" t="n"/>
-      <c r="O26" s="2" t="n"/>
-      <c r="P26" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>462</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>27772</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>505.5</v>
+      </c>
       <c r="Q26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" s="2" t="inlineStr"/>
-      <c r="S26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T06:17:42</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2010,14 +2412,32 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>463</v>
+      </c>
+      <c r="M27" t="n">
+        <v>13</v>
+      </c>
+      <c r="N27" t="n">
+        <v>17742</v>
+      </c>
+      <c r="O27" t="n">
+        <v>26</v>
+      </c>
+      <c r="P27" t="n">
+        <v>851.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>2026-09-20T06:31:54</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2064,14 +2484,32 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>464</v>
+      </c>
+      <c r="M28" t="n">
+        <v>23</v>
+      </c>
+      <c r="N28" t="n">
+        <v>36662</v>
+      </c>
+      <c r="O28" t="n">
+        <v>14</v>
+      </c>
+      <c r="P28" t="n">
+        <v>609.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>2026-09-20T06:42:04</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2118,19 +2556,33 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="n"/>
-      <c r="M29" s="2" t="n"/>
-      <c r="N29" s="2" t="n"/>
-      <c r="O29" s="2" t="n"/>
-      <c r="P29" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>465</v>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>18648</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>273.9</v>
+      </c>
       <c r="Q29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" s="2" t="inlineStr"/>
-      <c r="S29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T06:46:39</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2177,14 +2629,32 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>466</v>
+      </c>
+      <c r="M30" t="n">
+        <v>14</v>
+      </c>
+      <c r="N30" t="n">
+        <v>9890</v>
+      </c>
+      <c r="O30" t="n">
+        <v>20</v>
+      </c>
+      <c r="P30" t="n">
+        <v>204.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>2026-09-20T06:50:04</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2231,19 +2701,33 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="n"/>
-      <c r="M31" s="2" t="n"/>
-      <c r="N31" s="2" t="n"/>
-      <c r="O31" s="2" t="n"/>
-      <c r="P31" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>467</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>33865</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>436.9</v>
+      </c>
       <c r="Q31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" s="2" t="inlineStr"/>
-      <c r="S31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T06:57:21</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2290,14 +2774,32 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>468</v>
+      </c>
+      <c r="M32" t="n">
+        <v>11</v>
+      </c>
+      <c r="N32" t="n">
+        <v>15920</v>
+      </c>
+      <c r="O32" t="n">
+        <v>8</v>
+      </c>
+      <c r="P32" t="n">
+        <v>233.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>2026-09-20T07:01:15</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2344,19 +2846,33 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="n"/>
-      <c r="M33" s="2" t="n"/>
-      <c r="N33" s="2" t="n"/>
-      <c r="O33" s="2" t="n"/>
-      <c r="P33" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>469</v>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>15303</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>171</v>
+      </c>
       <c r="Q33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" s="2" t="inlineStr"/>
-      <c r="S33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T07:04:07</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2403,14 +2919,32 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>470</v>
+      </c>
+      <c r="M34" t="n">
+        <v>9</v>
+      </c>
+      <c r="N34" t="n">
+        <v>14600</v>
+      </c>
+      <c r="O34" t="n">
+        <v>9</v>
+      </c>
+      <c r="P34" t="n">
+        <v>166.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>2026-09-20T07:06:54</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2457,19 +2991,33 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="n"/>
-      <c r="M35" s="2" t="n"/>
-      <c r="N35" s="2" t="n"/>
-      <c r="O35" s="2" t="n"/>
-      <c r="P35" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>471</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>16704</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>206.3</v>
+      </c>
       <c r="Q35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" s="2" t="inlineStr"/>
-      <c r="S35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T07:10:21</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2516,14 +3064,32 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>472</v>
+      </c>
+      <c r="M36" t="n">
+        <v>6</v>
+      </c>
+      <c r="N36" t="n">
+        <v>6743</v>
+      </c>
+      <c r="O36" t="n">
+        <v>5</v>
+      </c>
+      <c r="P36" t="n">
+        <v>110.8</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>2026-09-20T07:12:12</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2570,19 +3136,33 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n"/>
-      <c r="M37" s="2" t="n"/>
-      <c r="N37" s="2" t="n"/>
-      <c r="O37" s="2" t="n"/>
-      <c r="P37" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>473</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>13600</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>165.4</v>
+      </c>
       <c r="Q37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" s="2" t="inlineStr"/>
-      <c r="S37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T07:14:58</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2629,14 +3209,32 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>474</v>
+      </c>
+      <c r="M38" t="n">
+        <v>8</v>
+      </c>
+      <c r="N38" t="n">
+        <v>11482</v>
+      </c>
+      <c r="O38" t="n">
+        <v>7</v>
+      </c>
+      <c r="P38" t="n">
+        <v>134.1</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>2026-09-20T07:17:13</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2683,19 +3281,33 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="n"/>
-      <c r="M39" s="2" t="n"/>
-      <c r="N39" s="2" t="n"/>
-      <c r="O39" s="2" t="n"/>
-      <c r="P39" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>475</v>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>13955</v>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>166.3</v>
+      </c>
       <c r="Q39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" s="2" t="inlineStr"/>
-      <c r="S39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T07:19:59</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2742,14 +3354,32 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>476</v>
+      </c>
+      <c r="M40" t="n">
+        <v>11</v>
+      </c>
+      <c r="N40" t="n">
+        <v>16291</v>
+      </c>
+      <c r="O40" t="n">
+        <v>7</v>
+      </c>
+      <c r="P40" t="n">
+        <v>185.1</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>2026-09-20T07:23:05</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2796,19 +3426,33 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="n"/>
-      <c r="M41" s="2" t="n"/>
-      <c r="N41" s="2" t="n"/>
-      <c r="O41" s="2" t="n"/>
-      <c r="P41" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>477</v>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>14821</v>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>172.4</v>
+      </c>
       <c r="Q41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" s="2" t="inlineStr"/>
-      <c r="S41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T07:25:58</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2855,14 +3499,32 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>478</v>
+      </c>
+      <c r="M42" t="n">
+        <v>11</v>
+      </c>
+      <c r="N42" t="n">
+        <v>17455</v>
+      </c>
+      <c r="O42" t="n">
+        <v>9</v>
+      </c>
+      <c r="P42" t="n">
+        <v>183.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2026-09-20T07:29:02</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2909,19 +3571,33 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="n"/>
-      <c r="M43" s="2" t="n"/>
-      <c r="N43" s="2" t="n"/>
-      <c r="O43" s="2" t="n"/>
-      <c r="P43" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>479</v>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>15120</v>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>165.4</v>
+      </c>
       <c r="Q43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T07:31:47</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2968,14 +3644,32 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>480</v>
+      </c>
+      <c r="M44" t="n">
+        <v>6</v>
+      </c>
+      <c r="N44" t="n">
+        <v>12237</v>
+      </c>
+      <c r="O44" t="n">
+        <v>9</v>
+      </c>
+      <c r="P44" t="n">
+        <v>259.5</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>2026-09-20T07:36:07</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3022,19 +3716,33 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n"/>
-      <c r="M45" s="2" t="n"/>
-      <c r="N45" s="2" t="n"/>
-      <c r="O45" s="2" t="n"/>
-      <c r="P45" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>481</v>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>26823</v>
+      </c>
+      <c r="O45" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="P45" s="2" t="n">
+        <v>493.9</v>
+      </c>
       <c r="Q45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" s="2" t="inlineStr"/>
-      <c r="S45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T07:44:22</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3081,14 +3789,32 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>482</v>
+      </c>
+      <c r="M46" t="n">
+        <v>10</v>
+      </c>
+      <c r="N46" t="n">
+        <v>19008</v>
+      </c>
+      <c r="O46" t="n">
+        <v>23</v>
+      </c>
+      <c r="P46" t="n">
+        <v>179.4</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>2026-09-20T07:47:22</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3135,19 +3861,33 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n"/>
-      <c r="M47" s="2" t="n"/>
-      <c r="N47" s="2" t="n"/>
-      <c r="O47" s="2" t="n"/>
-      <c r="P47" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>483</v>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>19465</v>
+      </c>
+      <c r="O47" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>280.1</v>
+      </c>
       <c r="Q47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" s="2" t="inlineStr"/>
-      <c r="S47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T07:52:02</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3194,14 +3934,32 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>484</v>
+      </c>
+      <c r="M48" t="n">
+        <v>11</v>
+      </c>
+      <c r="N48" t="n">
+        <v>15217</v>
+      </c>
+      <c r="O48" t="n">
+        <v>19</v>
+      </c>
+      <c r="P48" t="n">
+        <v>188.6</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>2026-09-20T07:55:11</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3248,14 +4006,32 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>485</v>
+      </c>
+      <c r="M49" t="n">
+        <v>16</v>
+      </c>
+      <c r="N49" t="n">
+        <v>31948</v>
+      </c>
+      <c r="O49" t="n">
+        <v>19</v>
+      </c>
+      <c r="P49" t="n">
+        <v>496.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>2026-09-20T08:03:29</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3302,19 +4078,33 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="n"/>
-      <c r="M50" s="2" t="n"/>
-      <c r="N50" s="2" t="n"/>
-      <c r="O50" s="2" t="n"/>
-      <c r="P50" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>486</v>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>15220</v>
+      </c>
+      <c r="O50" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>245.5</v>
+      </c>
       <c r="Q50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R50" s="2" t="inlineStr"/>
-      <c r="S50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T08:07:34</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3361,14 +4151,32 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>487</v>
+      </c>
+      <c r="M51" t="n">
+        <v>18</v>
+      </c>
+      <c r="N51" t="n">
+        <v>32205</v>
+      </c>
+      <c r="O51" t="n">
+        <v>24</v>
+      </c>
+      <c r="P51" t="n">
+        <v>979.4</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>2026-09-20T08:23:55</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3415,19 +4223,33 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n"/>
-      <c r="M52" s="2" t="n"/>
-      <c r="N52" s="2" t="n"/>
-      <c r="O52" s="2" t="n"/>
-      <c r="P52" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>488</v>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>25099</v>
+      </c>
+      <c r="O52" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>619.7</v>
+      </c>
       <c r="Q52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" s="2" t="inlineStr"/>
-      <c r="S52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T08:34:15</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3474,14 +4296,32 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>489</v>
+      </c>
+      <c r="M53" t="n">
+        <v>14</v>
+      </c>
+      <c r="N53" t="n">
+        <v>27701</v>
+      </c>
+      <c r="O53" t="n">
+        <v>13</v>
+      </c>
+      <c r="P53" t="n">
+        <v>531.3</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>2026-09-20T08:43:07</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3528,19 +4368,33 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="n"/>
-      <c r="M54" s="2" t="n"/>
-      <c r="N54" s="2" t="n"/>
-      <c r="O54" s="2" t="n"/>
-      <c r="P54" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>490</v>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>24617</v>
+      </c>
+      <c r="O54" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>254.6</v>
+      </c>
       <c r="Q54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R54" s="2" t="inlineStr"/>
-      <c r="S54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T08:47:22</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3587,14 +4441,32 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>491</v>
+      </c>
+      <c r="M55" t="n">
+        <v>16</v>
+      </c>
+      <c r="N55" t="n">
+        <v>28797</v>
+      </c>
+      <c r="O55" t="n">
+        <v>24</v>
+      </c>
+      <c r="P55" t="n">
+        <v>300.9</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>2026-09-20T08:52:23</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3641,19 +4513,33 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="n"/>
-      <c r="M56" s="2" t="n"/>
-      <c r="N56" s="2" t="n"/>
-      <c r="O56" s="2" t="n"/>
-      <c r="P56" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>492</v>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>31903</v>
+      </c>
+      <c r="O56" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>512.9</v>
+      </c>
       <c r="Q56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" s="2" t="inlineStr"/>
-      <c r="S56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T09:00:57</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3700,14 +4586,32 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>493</v>
+      </c>
+      <c r="M57" t="n">
+        <v>8</v>
+      </c>
+      <c r="N57" t="n">
+        <v>18469</v>
+      </c>
+      <c r="O57" t="n">
+        <v>7</v>
+      </c>
+      <c r="P57" t="n">
+        <v>173.2</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>2026-09-20T09:03:51</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3754,19 +4658,33 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="n"/>
-      <c r="M58" s="2" t="n"/>
-      <c r="N58" s="2" t="n"/>
-      <c r="O58" s="2" t="n"/>
-      <c r="P58" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>494</v>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>33806</v>
+      </c>
+      <c r="O58" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>327.8</v>
+      </c>
       <c r="Q58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R58" s="2" t="inlineStr"/>
-      <c r="S58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T09:09:19</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3813,14 +4731,32 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>495</v>
+      </c>
+      <c r="M59" t="n">
+        <v>13</v>
+      </c>
+      <c r="N59" t="n">
+        <v>26013</v>
+      </c>
+      <c r="O59" t="n">
+        <v>14</v>
+      </c>
+      <c r="P59" t="n">
+        <v>250.5</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>2026-09-20T09:13:30</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3867,19 +4803,33 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="n"/>
-      <c r="M60" s="2" t="n"/>
-      <c r="N60" s="2" t="n"/>
-      <c r="O60" s="2" t="n"/>
-      <c r="P60" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>23731</v>
+      </c>
+      <c r="O60" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="P60" s="2" t="n">
+        <v>243.6</v>
+      </c>
       <c r="Q60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R60" s="2" t="inlineStr"/>
-      <c r="S60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T09:17:34</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3926,14 +4876,32 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>497</v>
+      </c>
+      <c r="M61" t="n">
+        <v>14</v>
+      </c>
+      <c r="N61" t="n">
+        <v>29688</v>
+      </c>
+      <c r="O61" t="n">
+        <v>18</v>
+      </c>
+      <c r="P61" t="n">
+        <v>260.6</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>2026-09-20T09:21:55</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3980,19 +4948,33 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="n"/>
-      <c r="M62" s="2" t="n"/>
-      <c r="N62" s="2" t="n"/>
-      <c r="O62" s="2" t="n"/>
-      <c r="P62" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>498</v>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>25681</v>
+      </c>
+      <c r="O62" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>240.4</v>
+      </c>
       <c r="Q62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R62" s="2" t="inlineStr"/>
-      <c r="S62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T09:25:56</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4039,14 +5021,32 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>499</v>
+      </c>
+      <c r="M63" t="n">
+        <v>15</v>
+      </c>
+      <c r="N63" t="n">
+        <v>32711</v>
+      </c>
+      <c r="O63" t="n">
+        <v>21</v>
+      </c>
+      <c r="P63" t="n">
+        <v>285.8</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>2026-09-20T09:30:42</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4093,19 +5093,33 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="n"/>
-      <c r="M64" s="2" t="n"/>
-      <c r="N64" s="2" t="n"/>
-      <c r="O64" s="2" t="n"/>
-      <c r="P64" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>39351</v>
+      </c>
+      <c r="O64" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="P64" s="2" t="n">
+        <v>363.7</v>
+      </c>
       <c r="Q64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R64" s="2" t="inlineStr"/>
-      <c r="S64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T09:36:46</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4152,14 +5166,32 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>501</v>
+      </c>
+      <c r="M65" t="n">
+        <v>8</v>
+      </c>
+      <c r="N65" t="n">
+        <v>9388</v>
+      </c>
+      <c r="O65" t="n">
+        <v>2</v>
+      </c>
+      <c r="P65" t="n">
+        <v>152</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>2026-09-20T09:39:19</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4206,19 +5238,33 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="n"/>
-      <c r="M66" s="2" t="n"/>
-      <c r="N66" s="2" t="n"/>
-      <c r="O66" s="2" t="n"/>
-      <c r="P66" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>502</v>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>6579</v>
+      </c>
+      <c r="O66" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P66" s="2" t="n">
+        <v>121</v>
+      </c>
       <c r="Q66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R66" s="2" t="inlineStr"/>
-      <c r="S66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T09:41:20</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4265,14 +5311,32 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>503</v>
+      </c>
+      <c r="M67" t="n">
+        <v>3</v>
+      </c>
+      <c r="N67" t="n">
+        <v>1769</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1</v>
+      </c>
+      <c r="P67" t="n">
+        <v>49.5</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>2026-09-20T09:42:10</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4319,19 +5383,33 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="n"/>
-      <c r="M68" s="2" t="n"/>
-      <c r="N68" s="2" t="n"/>
-      <c r="O68" s="2" t="n"/>
-      <c r="P68" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>1713</v>
+      </c>
+      <c r="O68" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P68" s="2" t="n">
+        <v>45.7</v>
+      </c>
       <c r="Q68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R68" s="2" t="inlineStr"/>
-      <c r="S68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T09:42:56</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4378,14 +5456,32 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>505</v>
+      </c>
+      <c r="M69" t="n">
+        <v>11</v>
+      </c>
+      <c r="N69" t="n">
+        <v>10958</v>
+      </c>
+      <c r="O69" t="n">
+        <v>4</v>
+      </c>
+      <c r="P69" t="n">
+        <v>200.4</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>2026-09-20T09:46:17</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4432,19 +5528,33 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="n"/>
-      <c r="M70" s="2" t="n"/>
-      <c r="N70" s="2" t="n"/>
-      <c r="O70" s="2" t="n"/>
-      <c r="P70" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>506</v>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>5762</v>
+      </c>
+      <c r="O70" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P70" s="2" t="n">
+        <v>103.1</v>
+      </c>
       <c r="Q70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R70" s="2" t="inlineStr"/>
-      <c r="S70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T09:48:01</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4491,14 +5601,32 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>507</v>
+      </c>
+      <c r="M71" t="n">
+        <v>3</v>
+      </c>
+      <c r="N71" t="n">
+        <v>1776</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>54.7</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>2026-09-20T09:48:56</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4545,19 +5673,33 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="n"/>
-      <c r="M72" s="2" t="n"/>
-      <c r="N72" s="2" t="n"/>
-      <c r="O72" s="2" t="n"/>
-      <c r="P72" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>508</v>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N72" s="2" t="n">
+        <v>3316</v>
+      </c>
+      <c r="O72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="2" t="n">
+        <v>73.59999999999999</v>
+      </c>
       <c r="Q72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" s="2" t="inlineStr"/>
-      <c r="S72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T09:50:10</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4604,14 +5746,32 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>509</v>
+      </c>
+      <c r="M73" t="n">
+        <v>9</v>
+      </c>
+      <c r="N73" t="n">
+        <v>9472</v>
+      </c>
+      <c r="O73" t="n">
+        <v>3</v>
+      </c>
+      <c r="P73" t="n">
+        <v>156</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>2026-09-20T09:52:46</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -4658,19 +5818,33 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="n"/>
-      <c r="M74" s="2" t="n"/>
-      <c r="N74" s="2" t="n"/>
-      <c r="O74" s="2" t="n"/>
-      <c r="P74" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>510</v>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="N74" s="2" t="n">
+        <v>11974</v>
+      </c>
+      <c r="O74" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P74" s="2" t="n">
+        <v>235.1</v>
+      </c>
       <c r="Q74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R74" s="2" t="inlineStr"/>
-      <c r="S74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T09:56:42</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4717,14 +5891,32 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>511</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3</v>
+      </c>
+      <c r="N75" t="n">
+        <v>2336</v>
+      </c>
+      <c r="O75" t="n">
+        <v>2</v>
+      </c>
+      <c r="P75" t="n">
+        <v>53.5</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
-      </c>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>2026-09-20T09:57:36</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4771,19 +5963,33 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="n"/>
-      <c r="M76" s="2" t="n"/>
-      <c r="N76" s="2" t="n"/>
-      <c r="O76" s="2" t="n"/>
-      <c r="P76" s="2" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>512</v>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="N76" s="2" t="n">
+        <v>15183</v>
+      </c>
+      <c r="O76" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P76" s="2" t="n">
+        <v>238.4</v>
+      </c>
       <c r="Q76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R76" s="2" t="inlineStr"/>
-      <c r="S76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T10:01:35</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4830,14 +6036,33 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>513</v>
+      </c>
+      <c r="M77" t="n">
+        <v>7</v>
+      </c>
+      <c r="N77" t="n">
+        <v>7311</v>
+      </c>
+      <c r="O77" t="n">
+        <v>1</v>
+      </c>
+      <c r="P77" t="n">
+        <v>117.7</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>2026-09-20T10:03:33</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:S1"/>
